--- a/public/modeles/modele-devis.xlsx
+++ b/public/modeles/modele-devis.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="#  ##0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,34 +531,36 @@
       <c r="A24" t="str">
         <v>[Description détaillée de la prestation]</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" t="str">
-        <v>1 000,00</v>
+      <c r="C24">
+        <v>1000</v>
       </c>
       <c r="D24" t="str">
         <v>20 %</v>
       </c>
-      <c r="E24">
-        <f>IF(B24="","",B24*C24)</f>
+      <c r="E24" s="1">
+        <f>IF(B24="",0,B24*C24)</f>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
         <v>[Deuxième poste]</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B25">
         <v>2</v>
       </c>
-      <c r="C25" t="str">
-        <v>250,00</v>
+      <c r="C25">
+        <v>250</v>
       </c>
       <c r="D25" t="str">
         <v>20 %</v>
       </c>
-      <c r="E25">
-        <f>IF(B25="","",B25*C25)</f>
+      <c r="E25" s="1">
+        <f>IF(B25="",0,B25*C25)</f>
+        <v>500</v>
       </c>
     </row>
     <row r="26">
@@ -572,32 +576,36 @@
       <c r="D26" t="str">
         <v/>
       </c>
-      <c r="E26">
-        <f>IF(B26="","",B26*C26)</f>
+      <c r="E26" s="1">
+        <f>IF(B26="",0,B26*C26)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v>Total HT</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <f>SUM(E24:E26)</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v>TVA 20 %</v>
       </c>
-      <c r="B29" t="str">
-        <v>300,00</v>
+      <c r="B29" s="1">
+        <f>B28*0.2</f>
+        <v>300</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
         <v>Total TTC</v>
       </c>
-      <c r="B30" t="str">
-        <v>1 800,00</v>
+      <c r="B30" s="1">
+        <f>B28+B29</f>
+        <v>1800</v>
       </c>
     </row>
     <row r="31">
